--- a/design_issues/codescene/P5_ChartMaker.xlsx
+++ b/design_issues/codescene/P5_ChartMaker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="59">
   <si>
     <t>resource</t>
   </si>
@@ -149,12 +149,6 @@
   </si>
   <si>
     <t>Primitive Obsession ()</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments ()</t>
   </si>
   <si>
     <t>Complex Method (cc = 15)</t>
@@ -580,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="93.54296875" customWidth="1"/>
@@ -609,7 +603,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -626,7 +620,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -643,7 +637,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -660,7 +654,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -677,7 +671,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -694,7 +688,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -711,7 +705,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -728,7 +722,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -745,7 +739,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -762,7 +756,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -779,7 +773,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -796,7 +790,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -813,7 +807,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -830,7 +824,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -847,7 +841,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -864,7 +858,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -881,7 +875,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -898,7 +892,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -915,7 +909,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -932,7 +926,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
@@ -949,7 +943,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -966,7 +960,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -983,7 +977,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -1000,7 +994,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1017,7 +1011,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -1034,7 +1028,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -1051,7 +1045,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
@@ -1068,7 +1062,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1085,7 +1079,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
@@ -1102,7 +1096,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
@@ -1119,7 +1113,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -1136,7 +1130,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -1153,7 +1147,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -1170,7 +1164,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -1187,7 +1181,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -1204,7 +1198,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -1221,7 +1215,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
@@ -1238,7 +1232,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>7</v>
@@ -1255,7 +1249,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -1272,7 +1266,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -1289,7 +1283,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
@@ -1306,7 +1300,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -1323,7 +1317,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -1340,7 +1334,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
         <v>41</v>
@@ -1357,47 +1351,47 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="E47">
-        <v>277</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D48">
         <v>323</v>
@@ -1408,30 +1402,30 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D49">
-        <v>323</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>323</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1442,149 +1436,149 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E52">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D53">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D54">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="E54">
-        <v>90</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D55">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="E55">
-        <v>172</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D56">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="E56">
-        <v>245</v>
+        <v>302</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D57">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="E57">
-        <v>302</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D58">
-        <v>339</v>
+        <v>463</v>
       </c>
       <c r="E58">
-        <v>339</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D59">
         <v>463</v>
@@ -1595,30 +1589,30 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D60">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="E60">
-        <v>463</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D61">
         <v>502</v>
@@ -1629,7 +1623,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
         <v>35</v>
@@ -1638,15 +1632,15 @@
         <v>36</v>
       </c>
       <c r="D62">
-        <v>502</v>
+        <v>582</v>
       </c>
       <c r="E62">
-        <v>502</v>
+        <v>582</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
         <v>35</v>
@@ -1655,26 +1649,9 @@
         <v>36</v>
       </c>
       <c r="D63">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="E63">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64">
-        <v>601</v>
-      </c>
-      <c r="E64">
         <v>601</v>
       </c>
     </row>
@@ -1685,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:C14"/>
+  <dimension ref="A2:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36.08984375" customWidth="1"/>
@@ -1694,13 +1671,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1711,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIF(Issues!B2:B103,B3)</f>
+        <f>COUNTIF(Issues!B2:B102,B3)</f>
         <v>23</v>
       </c>
     </row>
@@ -1723,7 +1700,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIF(Issues!B2:B104,B4)</f>
+        <f>COUNTIF(Issues!B2:B103,B4)</f>
         <v>8</v>
       </c>
     </row>
@@ -1735,7 +1712,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIF(Issues!B2:B105,B5)</f>
+        <f>COUNTIF(Issues!B2:B104,B5)</f>
         <v>10</v>
       </c>
     </row>
@@ -1747,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIF(Issues!B2:B106,B6)</f>
+        <f>COUNTIF(Issues!B2:B105,B6)</f>
         <v>5</v>
       </c>
     </row>
@@ -1759,7 +1736,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIF(Issues!B2:B107,B7)</f>
+        <f>COUNTIF(Issues!B2:B106,B7)</f>
         <v>5</v>
       </c>
     </row>
@@ -1771,7 +1748,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIF(Issues!B2:B108,B8)</f>
+        <f>COUNTIF(Issues!B2:B107,B8)</f>
         <v>5</v>
       </c>
     </row>
@@ -1783,7 +1760,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIF(Issues!B2:B109,B9)</f>
+        <f>COUNTIF(Issues!B2:B108,B9)</f>
         <v>2</v>
       </c>
     </row>
@@ -1795,7 +1772,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIF(Issues!B2:B110,B10)</f>
+        <f>COUNTIF(Issues!B2:B109,B10)</f>
         <v>2</v>
       </c>
     </row>
@@ -1807,7 +1784,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIF(Issues!B2:B111,B11)</f>
+        <f>COUNTIF(Issues!B2:B110,B11)</f>
         <v>1</v>
       </c>
     </row>
@@ -1819,30 +1796,18 @@
         <v>9</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIF(Issues!B2:B112,B12)</f>
+        <f>COUNTIF(Issues!B2:B111,B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="2">
-        <f>COUNTIF(Issues!B2:B113,B13)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="3">
-        <f>SUM(C3:C13)</f>
-        <v>63</v>
+      <c r="A13" s="4"/>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3">
+        <f>SUM(C3:C12)</f>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
